--- a/out/MLP-mamba2_metrics.xlsx
+++ b/out/MLP-mamba2_metrics.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4219464242458343</v>
+        <v>0.4219464123249054</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3607150912284851</v>
+        <v>0.3607151210308075</v>
       </c>
       <c r="C2" t="n">
         <v>0.3188858330249786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.47723388671875</v>
+        <v>0.4772338807582855</v>
       </c>
       <c r="E2" t="n">
         <v>0.8506666666666668</v>
